--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7573.59</v>
+        <v>7598.5</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34174.31</v>
+        <v>34305.48</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11088.98</v>
+        <v>11103.2</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19000.69</v>
+        <v>19131.48</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6866.66</v>
+        <v>6911.88</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11910.56</v>
+        <v>11939.87</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11935.38</v>
+        <v>11970.13</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10365.67</v>
+        <v>10464.15</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35795.41</v>
+        <v>35906.08</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9606.58</v>
+        <v>9643.969999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5952-398-CM25</t>
+          <t>5855-188-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>76.050.859-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7598.5</v>
+        <v>8165.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5952-456-CM25</t>
+          <t>1774-131-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34305.48</v>
+        <v>9897.48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2366-4453-CM25</t>
+          <t>5952-398-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11103.2</v>
+        <v>7598.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1495200-5-CM25</t>
+          <t>5952-456-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19131.48</v>
+        <v>34305.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>542429-3-CM26</t>
+          <t>2366-4453-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6911.88</v>
+        <v>11103.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2585-122-CM26</t>
+          <t>1495200-5-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11939.87</v>
+        <v>19131.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5512-51-CM26</t>
+          <t>542429-3-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11970.13</v>
+        <v>6911.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5512-87-CM26</t>
+          <t>2585-122-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10464.15</v>
+        <v>11939.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2585-386-CM26</t>
+          <t>5512-51-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35906.08</v>
+        <v>11970.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5420-95-CM26</t>
+          <t>5512-87-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,6 +1118,128 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>10464.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2585-386-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>35906.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5420-95-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.978.890-7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>9643.969999999999</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5855-188-CM25</t>
+          <t>5358-43-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.251.000-3</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Camarones</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.050.859-4</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8165.93</v>
+        <v>24444.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1774-131-CM25</t>
+          <t>2585-228-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9897.48</v>
+        <v>9528.129999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5952-398-CM25</t>
+          <t>1260113-21-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7598.5</v>
+        <v>8458.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5952-456-CM25</t>
+          <t>5703-8-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>34305.48</v>
+        <v>28292.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2366-4453-CM25</t>
+          <t>1696-207-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11103.2</v>
+        <v>13916.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1495200-5-CM25</t>
+          <t>1346279-119-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>19131.48</v>
+        <v>26355.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>542429-3-CM26</t>
+          <t>5358-210-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6911.88</v>
+        <v>7445.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2585-122-CM26</t>
+          <t>5855-188-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>69.251.000-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD COMERCIAL DIQUALITA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.050.859-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11939.87</v>
+        <v>8165.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5512-51-CM26</t>
+          <t>1774-131-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11970.13</v>
+        <v>9897.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5512-87-CM26</t>
+          <t>1346279-126-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10464.15</v>
+        <v>31574.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2585-386-CM26</t>
+          <t>2366-4134-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35906.08</v>
+        <v>22744.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5420-95-CM26</t>
+          <t>5952-398-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,617 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
+        <v>7598.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5952-456-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>INDUMAC LTDA.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>34305.48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2366-4453-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>11103.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1495200-5-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>19131.48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>542429-3-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.979.490-7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>6911.88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2585-122-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>11939.87</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5512-51-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>IDEA MARKET SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.148.288-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>11970.13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5512-87-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>10464.15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2585-386-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>35906.08</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5420-95-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.978.890-7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>9643.969999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2366-488-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>45186.02</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5952-456-CM25</t>
+          <t>1053139-266-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>34305.48</v>
+        <v>35126.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2366-4453-CM25</t>
+          <t>5952-456-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11103.2</v>
+        <v>34305.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1495200-5-CM25</t>
+          <t>2366-4453-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>19131.48</v>
+        <v>11103.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>542429-3-CM26</t>
+          <t>1495200-5-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6911.88</v>
+        <v>19131.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2585-122-CM26</t>
+          <t>542429-3-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11939.87</v>
+        <v>6911.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5512-51-CM26</t>
+          <t>2585-122-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11970.13</v>
+        <v>11939.87</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5512-87-CM26</t>
+          <t>5512-51-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10464.15</v>
+        <v>11970.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2585-386-CM26</t>
+          <t>5512-87-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>35906.08</v>
+        <v>10464.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5420-95-CM26</t>
+          <t>2585-386-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9643.969999999999</v>
+        <v>35906.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2366-488-CM26</t>
+          <t>5420-95-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,7 +1850,129 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
+        <v>9643.969999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2366-488-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
         <v>45186.02</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5358-222-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>11204.03</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -562,7 +562,11 @@
           <t>77.285.439-0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2043,71 @@
         <v>11204.03</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5952-207-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>26921.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
